--- a/data/trans_dic/P21B_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21B_R2-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -722,57 +722,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 9,01</t>
+          <t>0,71; 8,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 17,22</t>
+          <t>2,73; 19,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,53</t>
+          <t>0,48; 3,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 10,35</t>
+          <t>2,43; 10,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,7</t>
+          <t>1,62; 6,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,83</t>
+          <t>0,86; 4,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,36</t>
+          <t>1,51; 6,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 10,04</t>
+          <t>2,68; 10,29</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,75</t>
+          <t>0,56; 4,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,35</t>
+          <t>0,54; 5,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 15,29</t>
+          <t>5,3; 15,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 9,74</t>
+          <t>2,24; 8,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,8</t>
+          <t>0,98; 4,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 8,13</t>
+          <t>2,17; 8,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,52</t>
+          <t>3,16; 8,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,88</t>
+          <t>1,11; 3,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,25</t>
+          <t>0,4; 2,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 9,91</t>
+          <t>4,28; 10,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,57</t>
+          <t>3,31; 7,13</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,41; 15,77</t>
+          <t>4,41; 15,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,4</t>
+          <t>1,04; 6,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 10,86</t>
+          <t>2,35; 11,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 14,2</t>
+          <t>5,34; 16,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 9,3</t>
+          <t>2,24; 9,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,59</t>
+          <t>1,63; 7,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 14,59</t>
+          <t>4,69; 14,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 12,1</t>
+          <t>7,11; 15,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 10,75</t>
+          <t>3,83; 10,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,93</t>
+          <t>1,86; 5,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 10,74</t>
+          <t>4,6; 11,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 11,2</t>
+          <t>7,45; 14,05</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 10,72</t>
+          <t>3,21; 11,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,98</t>
+          <t>0,59; 4,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 12,44</t>
+          <t>4,01; 12,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,7; 17,23</t>
+          <t>6,87; 16,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,62</t>
+          <t>1,65; 7,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 12,35</t>
+          <t>4,28; 11,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,08; 14,59</t>
+          <t>5,93; 14,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,76; 14,25</t>
+          <t>7,46; 14,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,93</t>
+          <t>2,6; 6,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,92</t>
+          <t>3,11; 7,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,13; 11,92</t>
+          <t>6,11; 12,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,59; 14,38</t>
+          <t>8,36; 13,72</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,27</t>
+          <t>2,59; 6,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,76</t>
+          <t>1,29; 3,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,34</t>
+          <t>4,74; 8,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,89; 10,51</t>
+          <t>5,95; 10,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,31</t>
+          <t>1,93; 4,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,42</t>
+          <t>2,09; 4,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,42</t>
+          <t>5,27; 9,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,64</t>
+          <t>6,4; 9,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,5</t>
+          <t>2,49; 4,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,76</t>
+          <t>2,08; 3,74</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 8,39</t>
+          <t>5,46; 8,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,4</t>
+          <t>6,6; 9,34</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13352</t>
+          <t>14364</t>
         </is>
       </c>
     </row>
@@ -1650,57 +1650,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1004; 12739</t>
+          <t>1010; 12308</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4676</t>
+          <t>0; 5158</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3186; 22150</t>
+          <t>3778; 27461</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4318</t>
+          <t>0; 4344</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>938; 8766</t>
+          <t>935; 7591</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3023; 14302</t>
+          <t>3353; 14952</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2353; 9594</t>
+          <t>2490; 9801</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3693</t>
+          <t>0; 4698</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2921; 16174</t>
+          <t>2887; 15722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3558; 15280</t>
+          <t>3615; 15412</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7772; 27273</t>
+          <t>7839; 30066</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10312</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>24125</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1050; 8822</t>
+          <t>1045; 8676</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1079; 9952</t>
+          <t>1245; 11516</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8963; 26231</t>
+          <t>9091; 26547</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5095; 20808</t>
+          <t>5259; 18778</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2728; 13618</t>
+          <t>2776; 14162</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5382</t>
+          <t>0; 6104</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3959; 17226</t>
+          <t>4591; 17902</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7859; 20116</t>
+          <t>8236; 22335</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4710; 18213</t>
+          <t>5216; 18301</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2052; 11910</t>
+          <t>2101; 12008</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16283; 38009</t>
+          <t>16425; 38908</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14745; 34049</t>
+          <t>16381; 35288</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11889</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19547</t>
+          <t>23445</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31437</t>
+          <t>38301</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5455; 19505</t>
+          <t>5449; 19270</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1802; 9826</t>
+          <t>1886; 11705</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3006; 13706</t>
+          <t>2967; 14029</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6462; 19818</t>
+          <t>8157; 24653</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3748; 16426</t>
+          <t>3958; 16631</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4302; 19572</t>
+          <t>4195; 19911</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7657; 22372</t>
+          <t>7182; 21909</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4367; 47155</t>
+          <t>15495; 34066</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11958; 32282</t>
+          <t>11505; 31333</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8166; 26099</t>
+          <t>8185; 24929</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11948; 30004</t>
+          <t>12846; 31099</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10033; 59274</t>
+          <t>27614; 52080</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>23526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>29431</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>52547</t>
+          <t>54696</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4389; 14623</t>
+          <t>4380; 15976</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>894; 7540</t>
+          <t>892; 7560</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6450; 18882</t>
+          <t>6085; 19510</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14969; 33479</t>
+          <t>14212; 34518</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3740; 15066</t>
+          <t>3758; 16592</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9812; 27987</t>
+          <t>9699; 26825</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14963; 35876</t>
+          <t>14574; 34646</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21525; 39547</t>
+          <t>22543; 42386</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10338; 25214</t>
+          <t>9466; 25338</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11402; 29942</t>
+          <t>11773; 29471</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24392; 47397</t>
+          <t>24305; 47987</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40541; 67846</t>
+          <t>42558; 69838</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53665</t>
+          <t>57833</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>66627</t>
+          <t>73654</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>120292</t>
+          <t>131486</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15263; 35006</t>
+          <t>14448; 35954</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9291; 26442</t>
+          <t>9048; 25751</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26552; 51514</t>
+          <t>26160; 49407</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39799; 71077</t>
+          <t>43599; 79154</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15672; 35543</t>
+          <t>15880; 35103</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20624; 43213</t>
+          <t>20445; 44572</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39491; 70597</t>
+          <t>39470; 71959</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>35499; 90445</t>
+          <t>59838; 90891</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33647; 62143</t>
+          <t>34462; 62244</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34503; 63203</t>
+          <t>35008; 62867</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71145; 109142</t>
+          <t>70960; 109790</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>79066; 144678</t>
+          <t>110035; 155707</t>
         </is>
       </c>
     </row>
